--- a/Project Outputs for UZ_A_DAC/Rev02/BOM/BOM_JLC-UZ_A_DAC(THS)_FR.xlsx
+++ b/Project Outputs for UZ_A_DAC/Rev02/BOM/BOM_JLC-UZ_A_DAC(THS)_FR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20413"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\altium\uz_a_dac8831\Project Outputs for UZ_A_DAC\Rev02\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ga92wum\git\UltraZohm\PCB\uz_a_dac8831\Project Outputs for UZ_A_DAC\Rev02\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{631CA588-28A9-4278-86C8-654714C89A65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFCCAC50-4BDE-41F7-8851-31E305B650C2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15090" yWindow="-16125" windowWidth="19350" windowHeight="7560" xr2:uid="{8EB92CD4-8990-4A58-AC57-FDF9BBF21F69}"/>
+    <workbookView xWindow="15090" yWindow="-16130" windowWidth="19350" windowHeight="7560" xr2:uid="{8EB92CD4-8990-4A58-AC57-FDF9BBF21F69}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM_JLC-UZ_A_DAC(THS)" sheetId="1" r:id="rId1"/>
@@ -23,21 +23,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="331">
   <si>
     <t>Quantity</t>
   </si>
@@ -1024,6 +1015,12 @@
   </si>
   <si>
     <t>DAC8831IDR</t>
+  </si>
+  <si>
+    <t>C5250961</t>
+  </si>
+  <si>
+    <t>Bauteil Original</t>
   </si>
 </sst>
 </file>
@@ -1039,7 +1036,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1055,6 +1052,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1095,7 +1098,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
@@ -1111,6 +1114,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1425,23 +1429,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA835F02-90E0-46D5-96C3-B9AA0DEAF99F}">
-  <dimension ref="A1:M60"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:N60"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.265625" customWidth="1"/>
-    <col min="2" max="2" width="18.53125" customWidth="1"/>
-    <col min="3" max="3" width="17.06640625" customWidth="1"/>
+    <col min="1" max="1" width="9.26953125" customWidth="1"/>
+    <col min="2" max="2" width="18.54296875" customWidth="1"/>
+    <col min="3" max="3" width="17.08984375" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" customWidth="1"/>
-    <col min="6" max="6" width="54.06640625" customWidth="1"/>
-    <col min="7" max="7" width="23.53125" customWidth="1"/>
-    <col min="8" max="8" width="8.46484375" customWidth="1"/>
-    <col min="9" max="9" width="9.73046875" customWidth="1"/>
-    <col min="10" max="10" width="27.9296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.36328125" customWidth="1"/>
+    <col min="6" max="6" width="54.08984375" customWidth="1"/>
+    <col min="7" max="7" width="23.54296875" customWidth="1"/>
+    <col min="8" max="8" width="8.453125" customWidth="1"/>
+    <col min="9" max="9" width="9.7265625" customWidth="1"/>
+    <col min="10" max="10" width="27.90625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1478,8 +1482,11 @@
       <c r="L1" s="4" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="N1" s="4" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>71</v>
       </c>
@@ -1510,7 +1517,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>23</v>
       </c>
@@ -1541,7 +1548,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -1572,7 +1579,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>5</v>
       </c>
@@ -1603,7 +1610,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -1634,7 +1641,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -1665,7 +1672,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -1696,7 +1703,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -1727,7 +1734,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>23</v>
       </c>
@@ -1758,7 +1765,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>1</v>
       </c>
@@ -1789,7 +1796,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>16</v>
       </c>
@@ -1820,7 +1827,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>1</v>
       </c>
@@ -1848,11 +1855,13 @@
         <v>71</v>
       </c>
       <c r="K13" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="N13" s="13" t="s">
         <v>308</v>
       </c>
-      <c r="M13" s="11"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.45">
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>6</v>
       </c>
@@ -1884,7 +1893,7 @@
       </c>
       <c r="M14" s="11"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>1</v>
       </c>
@@ -1911,17 +1920,17 @@
       <c r="J15" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="K15" s="1" t="s">
-        <v>301</v>
+      <c r="K15" s="12" t="s">
+        <v>311</v>
       </c>
       <c r="L15" s="10" t="s">
         <v>309</v>
       </c>
-      <c r="M15" s="12" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="N15" s="1" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>1</v>
       </c>
@@ -1954,7 +1963,7 @@
       <c r="L16" s="10"/>
       <c r="M16" s="11"/>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -1984,7 +1993,7 @@
       </c>
       <c r="M17" s="11"/>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>1</v>
       </c>
@@ -2014,7 +2023,7 @@
       </c>
       <c r="M18" s="11"/>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>1</v>
       </c>
@@ -2044,7 +2053,7 @@
       </c>
       <c r="M19" s="11"/>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>1</v>
       </c>
@@ -2074,7 +2083,7 @@
       </c>
       <c r="M20" s="11"/>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>1</v>
       </c>
@@ -2101,17 +2110,17 @@
       <c r="J21" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="K21" s="8" t="s">
-        <v>293</v>
+      <c r="K21" s="12" t="s">
+        <v>321</v>
       </c>
       <c r="L21" t="s">
         <v>322</v>
       </c>
-      <c r="M21" s="12" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="N21" s="8" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>2</v>
       </c>
@@ -2143,7 +2152,7 @@
       </c>
       <c r="M22" s="11"/>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>1</v>
       </c>
@@ -2174,7 +2183,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>1</v>
       </c>
@@ -2203,7 +2212,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>2</v>
       </c>
@@ -2234,7 +2243,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>1</v>
       </c>
@@ -2265,7 +2274,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>2</v>
       </c>
@@ -2296,7 +2305,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>1</v>
       </c>
@@ -2327,7 +2336,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>1</v>
       </c>
@@ -2358,7 +2367,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>1</v>
       </c>
@@ -2389,7 +2398,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>1</v>
       </c>
@@ -2420,7 +2429,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>25</v>
       </c>
@@ -2451,7 +2460,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>1</v>
       </c>
@@ -2482,7 +2491,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>1</v>
       </c>
@@ -2513,7 +2522,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
         <v>1</v>
       </c>
@@ -2544,7 +2553,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
         <v>1</v>
       </c>
@@ -2575,7 +2584,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
         <v>1</v>
       </c>
@@ -2606,7 +2615,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
         <v>2</v>
       </c>
@@ -2637,7 +2646,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
         <v>1</v>
       </c>
@@ -2668,7 +2677,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
         <v>16</v>
       </c>
@@ -2699,7 +2708,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
         <v>16</v>
       </c>
@@ -2730,7 +2739,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
         <v>34</v>
       </c>
@@ -2761,7 +2770,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
         <v>2</v>
       </c>
@@ -2788,17 +2797,17 @@
       <c r="J43" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="K43" s="8" t="s">
-        <v>280</v>
+      <c r="K43" s="9" t="s">
+        <v>324</v>
       </c>
       <c r="L43" t="s">
         <v>323</v>
       </c>
-      <c r="M43" s="9" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="N43" s="8" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
         <v>1</v>
       </c>
@@ -2829,7 +2838,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
         <v>8</v>
       </c>
@@ -2860,7 +2869,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A46" s="1">
         <v>16</v>
       </c>
@@ -2887,17 +2896,17 @@
       <c r="J46" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="K46" s="8" t="s">
-        <v>279</v>
+      <c r="K46" s="9" t="s">
+        <v>326</v>
       </c>
       <c r="L46" t="s">
         <v>325</v>
       </c>
-      <c r="M46" s="9" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="N46" s="8" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
         <v>2</v>
       </c>
@@ -2928,7 +2937,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A48" s="1">
         <v>1</v>
       </c>
@@ -2959,7 +2968,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A49" s="1">
         <v>1</v>
       </c>
@@ -2988,7 +2997,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A50" s="1">
         <v>1</v>
       </c>
@@ -3017,7 +3026,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A51" s="1">
         <v>1</v>
       </c>
@@ -3046,7 +3055,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A52" s="1">
         <v>1</v>
       </c>
@@ -3075,7 +3084,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A53" s="1">
         <v>1</v>
       </c>
@@ -3104,7 +3113,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A54" s="1">
         <v>1</v>
       </c>
@@ -3133,7 +3142,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A55" s="1">
         <v>1</v>
       </c>
@@ -3162,7 +3171,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A56" s="1">
         <v>8</v>
       </c>
@@ -3191,7 +3200,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A57" s="1">
         <v>8</v>
       </c>
@@ -3220,7 +3229,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A58" s="1">
         <v>8</v>
       </c>
@@ -3245,17 +3254,17 @@
       <c r="J58" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="K58" s="8" t="s">
-        <v>267</v>
+      <c r="K58" s="9" t="s">
+        <v>327</v>
       </c>
       <c r="L58" t="s">
         <v>328</v>
       </c>
-      <c r="M58" s="9" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="N58" s="8" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A59" s="1">
         <v>2</v>
       </c>
@@ -3284,7 +3293,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A60" s="1">
         <v>1</v>
       </c>
